--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>10/08 13:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>09/08 23:45</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>55</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>11/08 22:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>08/08 18:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>03/08 23:20</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>10/08 20:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>03/08 23:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>60</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>03/08 22:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>60</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>09/08 00:15</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>60</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>08/08 10:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>60</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>03/08 18:15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>60</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>09/08 16:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>40</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>03/08 15:25</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>40</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>50</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>45</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>09/08 18:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>50</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>04/08 01:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>40</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>03/08 11:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.18</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>12/08 18:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>55</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>03/08 17:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>40</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>03/08 22:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F26" t="n">
+        <v>2.15</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,142 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45872.08906479059</v>
+        <v>45872.08906479167</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Tecnico Un</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario – Manta FCSerie A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>03/08 20:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+8,46%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45872.1742029329</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Corinthian</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Corinthians – FortalezaSérie A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+6,78%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45872.1742029329</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 14.5 - tirs1re équipe | Genk – Anv</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Genk – AnversBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Moins que 14.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>03/08 11:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>38,9%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+5,12%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45872.1742029329</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>03/08 20:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>40</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45872.1742029329</v>
+        <v>45872.17420292824</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>45</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45872.1742029329</v>
+        <v>45872.17420292824</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>03/08 11:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.7</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,142 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45872.1742029329</v>
+        <v>45872.17420292824</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Hajduk Spl</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hajduk Split – Istra 1961HNL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+50,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45872.22867913067</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dalian Zhi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Dalian Zhixing FC – Qingdao Hainiu FCSuper League</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>03/08 11:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45872.22867913067</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Hamrun Spa</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hamrun Spartans FC – Maccabi Tel AvivLigue Europa</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>05/08 17:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+9,94%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45872.22867913067</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>60</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45872.22867913067</v>
+        <v>45872.22867913194</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>03/08 11:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>50</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45872.22867913067</v>
+        <v>45872.22867913194</v>
       </c>
     </row>
     <row r="32">
@@ -1799,23 +1795,156 @@
           <t>05/08 17:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>50</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+9,94%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45872.22867913194</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Santos – J</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Santos – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>04/08 23:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>41,7%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+25,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45872.27328912776</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Shamrock R</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers – Derry CityPremier Division</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>03/08 18:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2,20%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>+9,94%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>45872.22867913067</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+24,7%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45872.27328912776</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Pas de buts | Seinajoen </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Seinajoen JK – FC KTPVeikkausliiga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>03/08 13:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>26.50</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+7,16%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45872.27328912776</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>04/08 23:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45872.27328912776</v>
+        <v>45872.27328913195</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>03/08 18:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>50</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45872.27328912776</v>
+        <v>45872.27328913195</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>03/08 13:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>26.50</t>
-        </is>
+      <c r="F35" t="n">
+        <v>26.5</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,52 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45872.27328912776</v>
+        <v>45872.27328913195</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Jiri Lehec</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka – Taylor FritzATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>04/08 00:10</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>81,4%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+5,77%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45872.30681523398</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>04/08 00:10</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="F36" t="n">
+        <v>1.3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,97 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45872.30681523398</v>
+        <v>45872.30681523148</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 25.5 - tirs | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Botafogo – CruzeiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>34,3%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+9,62%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45872.35344512156</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | KS Cracovi</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>KS Cracovia – Lechia GdanskPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>03/08 12:45</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>46,7%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+8,88%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45872.35344512156</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F37" t="n">
+        <v>3.2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45872.35344512156</v>
+        <v>45872.35344512732</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>03/08 12:45</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
+      <c r="F38" t="n">
+        <v>2.33</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,97 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45872.35344512156</v>
+        <v>45872.35344512732</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 7.5 - tir cadré1re équipe | Santos – J</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Santos – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 7.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>04/08 23:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>35,3%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+16,4%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45872.3913359318</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC Pacos F</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FC Pacos Ferreira – FC VizelaPortugal, Segunda Liga stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>09/08 10:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+4,68%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45872.3913359318</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -2096,10 +2096,8 @@
           <t>04/08 23:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F39" t="n">
+        <v>3.3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45872.3913359318</v>
+        <v>45872.3913359375</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>09/08 10:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>35</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45872.3913359318</v>
+        <v>45872.3913359375</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2156,6 +2156,96 @@
         <v>45872.3913359375</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Univers</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FC Universitatea Cluj – FC Petrolul PloiestiLiga 1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>09/08 18:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+53,1%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45872.47245534581</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set2e participant | Clara Taus</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Clara Tauson – Iga SwiatekWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>03/08 22:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+2,53%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45872.47245534581</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>09/08 18:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>60</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45872.47245534581</v>
+        <v>45872.47245534722</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>03/08 22:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
+      <c r="F42" t="n">
+        <v>4.9</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,142 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45872.47245534581</v>
+        <v>45872.47245534722</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set2e participant | Frances Ti</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Frances Tiafoe – Alex De MinaurATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>03/08 16:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>18,6%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+9,71%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45872.53359511108</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | EC Bahia –</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EC Bahia – FluminenseSérie A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10/08 00:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+6,51%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45872.53359511108</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Newell's O</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys – Central CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>09/08 00:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+2,11%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45872.53359511108</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>03/08 16:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
+      <c r="F43" t="n">
+        <v>5.9</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45872.53359511108</v>
+        <v>45872.53359511574</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>10/08 00:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>50</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45872.53359511108</v>
+        <v>45872.53359511574</v>
       </c>
     </row>
     <row r="45">
@@ -2358,23 +2354,156 @@
           <t>09/08 00:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>40</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+2,11%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45872.53359511574</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – Arka GdyniaPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>03/08 18:15</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>45,3%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+6,54%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45872.56574540843</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tir cadré | Atletico M</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – BragantinoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>03/08 21:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>27,6%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+5,04%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45872.56574540843</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Boca Junio</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Boca Juniors – Racing ClubLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>09/08 19:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>+2,11%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>45872.53359511108</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+3,09%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45872.56574540843</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>03/08 18:15</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.35</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45872.56574540843</v>
+        <v>45872.5657454051</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="F47" t="n">
+        <v>3.8</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45872.56574540843</v>
+        <v>45872.5657454051</v>
       </c>
     </row>
     <row r="48">
@@ -2487,10 +2483,8 @@
           <t>09/08 19:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>40</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2503,7 +2497,52 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45872.56574540843</v>
+        <v>45872.5657454051</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1(0:1) | Larne – Sa</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Larne – Santa ClaraEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1(0:1)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>07/08 19:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+20,7%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45872.59766816731</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>07/08 19:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>22</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,52 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45872.59766816731</v>
+        <v>45872.59766817129</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Golden Sta</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries – Las Vegas AcesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>03/08 22:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+4,49%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45872.6412782206</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>03/08 22:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>20</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,52 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45872.6412782206</v>
+        <v>45872.64127821759</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Slovan </t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FC Slovan Liberec – FK Dukla PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>09/08 15:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+4,68%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45872.68639855009</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>40</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,97 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45872.68639855009</v>
+        <v>45872.68639855324</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 16.5 - tirs1re équipe | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – Arka GdyniaPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>03/08 18:15</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+11,2%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45872.72284424825</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | St Patrick</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>St Patricks Athletic – BesiktasEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>07/08 18:45</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+4,84%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45872.72284424825</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>03/08 18:15</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.22</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45872.72284424825</v>
+        <v>45872.72284424768</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>07/08 18:45</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="F53" t="n">
+        <v>7.5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,232 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45872.72284424825</v>
+        <v>45872.72284424768</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | NK Osijek </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NK Osijek – HNK RijekaHNL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>09/08 19:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+38,8%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45872.77276562557</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Hradec </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove – FK PardubiceSynot League</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>10/08 13:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+34,5%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45872.77276562557</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Sparta Prague – SK Sigma OlomoucSynot League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>10/08 18:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+27,3%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45872.77276562557</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Once Calda</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Once Caldas – Rionegro AguilasPrimera A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>09/08 20:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+7,30%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45872.77276562557</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Uniao de L</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Uniao de Leiria – Académico de ViseuPortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>10/08 17:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+4,14%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45872.77276562557</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>09/08 19:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>50</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45872.77276562557</v>
+        <v>45872.772765625</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>10/08 13:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>55</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45872.77276562557</v>
+        <v>45872.772765625</v>
       </c>
     </row>
     <row r="56">
@@ -2831,10 +2827,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>50</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2847,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45872.77276562557</v>
+        <v>45872.772765625</v>
       </c>
     </row>
     <row r="57">
@@ -2876,10 +2870,8 @@
           <t>09/08 20:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>40</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2892,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45872.77276562557</v>
+        <v>45872.772765625</v>
       </c>
     </row>
     <row r="58">
@@ -2921,10 +2913,8 @@
           <t>10/08 17:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>35</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2937,7 +2927,97 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45872.77276562557</v>
+        <v>45872.772765625</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Sanfrecce </t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima – Shimizu S-P.J-League</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>10/08 09:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+25,9%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45872.80491978444</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Levski Sof</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Levski Sofia – Spartak VarnaBulgarie. Bulgarie - Parva Liga</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>10/08 16:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+24,8%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45872.80491978444</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>10/08 09:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>60</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45872.80491978444</v>
+        <v>45872.80491978009</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>10/08 16:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>22</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,142 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45872.80491978444</v>
+        <v>45872.80491978009</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Cerro Port</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Cerro Porteno – Nacional AsuncionPrimera Division</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>08/08 21:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+62,9%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45872.85141737171</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Alianza FC</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar – Atlético BucaramangaPrimera A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>03/08 21:10</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+17,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45872.85141737171</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Sport</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Club Sportivo Luqueno – CA Tembetary YpanePrimera Division</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>09/08 21:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+6,28%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45872.85141737171</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>08/08 21:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>60</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45872.85141737171</v>
+        <v>45872.85141737269</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>03/08 21:10</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>50</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45872.85141737171</v>
+        <v>45872.85141737269</v>
       </c>
     </row>
     <row r="63">
@@ -3132,10 +3128,8 @@
           <t>09/08 21:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>35</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3148,7 +3142,97 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45872.85141737171</v>
+        <v>45872.85141737269</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Internacio</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Internacional RS – Sao Paulo SPBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>03/08 23:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+5,33%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45872.89027585596</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | A.Anisimov</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>A.Anisimova – E.SvitolinaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>03/08 23:10</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>68,7%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+3,00%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45872.89027585596</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>03/08 23:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F64" t="n">
+        <v>2.4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45872.89027585596</v>
+        <v>45872.89027585648</v>
       </c>
     </row>
     <row r="65">
@@ -3216,10 +3214,8 @@
           <t>03/08 23:10</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="F65" t="n">
+        <v>1.5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3232,7 +3228,97 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45872.89027585596</v>
+        <v>45872.89027585648</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Metalist 1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Metalist 1925 Kharkiv – FC Obolon KievUPL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>04/08 15:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+20,4%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45872.9326895593</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set2e participant | Flavio Cob</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Flavio Cobolli – Ben SheltonATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>03/08 23:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+4,51%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45872.9326895593</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-03.xlsx
+++ b/data/valuebets_database_2025-08-03.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>04/08 15:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>45</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45872.9326895593</v>
+        <v>45872.93268956018</v>
       </c>
     </row>
     <row r="67">
@@ -3302,10 +3300,8 @@
           <t>03/08 23:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
+      <c r="F67" t="n">
+        <v>4.7</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3318,7 +3314,52 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45872.9326895593</v>
+        <v>45872.93268956018</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Ilves –</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FC Ilves – IF GnistanVeikkausliiga</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>04/08 15:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,40%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+7,87%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45872.97456439336</v>
       </c>
     </row>
   </sheetData>
